--- a/outputs/Block6C_Probability_Snapshot.xlsx
+++ b/outputs/Block6C_Probability_Snapshot.xlsx
@@ -408,7 +408,7 @@
         <v>2</v>
       </c>
       <c r="B2">
-        <v>74.58</v>
+        <v>92.2</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -416,7 +416,7 @@
         <v>3</v>
       </c>
       <c r="B3">
-        <v>25.42</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -424,7 +424,7 @@
         <v>4</v>
       </c>
       <c r="B4">
-        <v>22.54</v>
+        <v>43.04</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -432,7 +432,7 @@
         <v>5</v>
       </c>
       <c r="B5">
-        <v>77.45999999999999</v>
+        <v>56.96</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -440,7 +440,7 @@
         <v>6</v>
       </c>
       <c r="B6">
-        <v>16.12</v>
+        <v>20.17</v>
       </c>
     </row>
   </sheetData>
